--- a/VerveStacks_NGA_grids_kan/SysSettings.xlsx
+++ b/VerveStacks_NGA_grids_kan/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NGA_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5548A24B-9396-4B9C-87B0-1D4F089E81D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DDEC772-04FB-4574-AF08-C2D365BFA071}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5963,7 +5963,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{652214C7-D9CA-4847-BBF5-7FE84A8E77C0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04D0B2DE-5450-4AA7-B827-A13F913A68AE}">
   <dimension ref="B3:H66"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_NGA_grids_kan/SysSettings.xlsx
+++ b/VerveStacks_NGA_grids_kan/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NGA_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DDEC772-04FB-4574-AF08-C2D365BFA071}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{112409B4-05B4-4B75-BEB6-4D9DBCEFF7E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5963,7 +5963,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04D0B2DE-5450-4AA7-B827-A13F913A68AE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DB2CE0F-8265-4DE5-AD88-B8FF4AEAA4A4}">
   <dimension ref="B3:H66"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_NGA_grids_kan/SysSettings.xlsx
+++ b/VerveStacks_NGA_grids_kan/SysSettings.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NGA_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{112409B4-05B4-4B75-BEB6-4D9DBCEFF7E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{036B175F-7896-4B04-B4EB-2B77E7DBF217}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5963,7 +5963,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DB2CE0F-8265-4DE5-AD88-B8FF4AEAA4A4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD3EBDFF-7F61-4D12-AA63-38733C37FC34}">
   <dimension ref="B3:H66"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_NGA_grids_kan/SysSettings.xlsx
+++ b/VerveStacks_NGA_grids_kan/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NGA_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{036B175F-7896-4B04-B4EB-2B77E7DBF217}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{721B4D8A-CAD5-4402-A5AA-6B7C76A8F57E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5963,7 +5963,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD3EBDFF-7F61-4D12-AA63-38733C37FC34}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E76E5488-4E38-4FD7-B484-20D8479AFFBE}">
   <dimension ref="B3:H66"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_NGA_grids_kan/SysSettings.xlsx
+++ b/VerveStacks_NGA_grids_kan/SysSettings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NGA_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{721B4D8A-CAD5-4402-A5AA-6B7C76A8F57E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{991A1C64-E7FE-4F76-85C2-891FDB95A82C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1433" uniqueCount="488">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1440" uniqueCount="494">
   <si>
     <t>~BookRegions_Map</t>
   </si>
@@ -1503,6 +1503,24 @@
   </si>
   <si>
     <t>grid node -- way/836122563-330</t>
+  </si>
+  <si>
+    <t>~tfm_comgrp</t>
+  </si>
+  <si>
+    <t>allregions</t>
+  </si>
+  <si>
+    <t>cset_cn</t>
+  </si>
+  <si>
+    <t>ELC,e[_]*</t>
+  </si>
+  <si>
+    <t>y</t>
+  </si>
+  <si>
+    <t>ELC_BatIn</t>
   </si>
 </sst>
 </file>
@@ -4657,6 +4675,9 @@
       </c>
     </row>
     <row r="27" spans="2:18">
+      <c r="B27" t="s">
+        <v>488</v>
+      </c>
       <c r="M27" t="s">
         <v>17</v>
       </c>
@@ -4677,6 +4698,15 @@
       </c>
     </row>
     <row r="28" spans="2:18">
+      <c r="B28" t="s">
+        <v>173</v>
+      </c>
+      <c r="C28" t="s">
+        <v>489</v>
+      </c>
+      <c r="D28" t="s">
+        <v>490</v>
+      </c>
       <c r="M28" t="s">
         <v>17</v>
       </c>
@@ -4697,6 +4727,15 @@
       </c>
     </row>
     <row r="29" spans="2:18">
+      <c r="B29" t="s">
+        <v>493</v>
+      </c>
+      <c r="C29" t="s">
+        <v>492</v>
+      </c>
+      <c r="D29" t="s">
+        <v>491</v>
+      </c>
       <c r="M29" t="s">
         <v>17</v>
       </c>

--- a/VerveStacks_NGA_grids_kan/SysSettings.xlsx
+++ b/VerveStacks_NGA_grids_kan/SysSettings.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NGA_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{991A1C64-E7FE-4F76-85C2-891FDB95A82C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2775E1F-AF69-4C07-8127-8EDB4CE9DC29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
-    <sheet name="fuels" sheetId="2" r:id="rId2"/>
-    <sheet name="TimePeriods" sheetId="3" r:id="rId3"/>
-    <sheet name="grids" sheetId="7" r:id="rId4"/>
+    <sheet name="grids" sheetId="7" r:id="rId2"/>
+    <sheet name="fuels" sheetId="2" r:id="rId3"/>
+    <sheet name="TimePeriods" sheetId="3" r:id="rId4"/>
     <sheet name="System Settings" sheetId="4" r:id="rId5"/>
     <sheet name="Constants" sheetId="5" r:id="rId6"/>
     <sheet name="reporting options" sheetId="6" r:id="rId7"/>
@@ -680,6 +680,24 @@
     <t>cap_bnd</t>
   </si>
   <si>
+    <t>~tfm_comgrp</t>
+  </si>
+  <si>
+    <t>allregions</t>
+  </si>
+  <si>
+    <t>cset_cn</t>
+  </si>
+  <si>
+    <t>ELC,e[_]*</t>
+  </si>
+  <si>
+    <t>y</t>
+  </si>
+  <si>
+    <t>ELC_BatIn</t>
+  </si>
+  <si>
     <t>NGA</t>
   </si>
   <si>
@@ -1503,24 +1521,6 @@
   </si>
   <si>
     <t>grid node -- way/836122563-330</t>
-  </si>
-  <si>
-    <t>~tfm_comgrp</t>
-  </si>
-  <si>
-    <t>allregions</t>
-  </si>
-  <si>
-    <t>cset_cn</t>
-  </si>
-  <si>
-    <t>ELC,e[_]*</t>
-  </si>
-  <si>
-    <t>y</t>
-  </si>
-  <si>
-    <t>ELC_BatIn</t>
   </si>
 </sst>
 </file>
@@ -3911,7 +3911,7 @@
         <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="F4" t="s">
         <v>36</v>
@@ -3935,6 +3935,1470 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E833400-FB26-49F4-9409-80FCE2D46259}">
+  <dimension ref="B3:H66"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetData>
+    <row r="3" spans="2:8">
+      <c r="B3" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8">
+      <c r="B4" t="s">
+        <v>220</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8">
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s">
+        <v>369</v>
+      </c>
+      <c r="D5" t="s">
+        <v>370</v>
+      </c>
+      <c r="E5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" t="s">
+        <v>35</v>
+      </c>
+      <c r="G5" t="s">
+        <v>371</v>
+      </c>
+      <c r="H5" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8">
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="s">
+        <v>372</v>
+      </c>
+      <c r="D6" t="s">
+        <v>373</v>
+      </c>
+      <c r="E6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" t="s">
+        <v>35</v>
+      </c>
+      <c r="G6" t="s">
+        <v>371</v>
+      </c>
+      <c r="H6" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8">
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" t="s">
+        <v>374</v>
+      </c>
+      <c r="D7" t="s">
+        <v>375</v>
+      </c>
+      <c r="E7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" t="s">
+        <v>35</v>
+      </c>
+      <c r="G7" t="s">
+        <v>371</v>
+      </c>
+      <c r="H7" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8">
+      <c r="B8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" t="s">
+        <v>376</v>
+      </c>
+      <c r="D8" t="s">
+        <v>377</v>
+      </c>
+      <c r="E8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8" t="s">
+        <v>35</v>
+      </c>
+      <c r="G8" t="s">
+        <v>371</v>
+      </c>
+      <c r="H8" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8">
+      <c r="B9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" t="s">
+        <v>378</v>
+      </c>
+      <c r="D9" t="s">
+        <v>379</v>
+      </c>
+      <c r="E9" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9" t="s">
+        <v>35</v>
+      </c>
+      <c r="G9" t="s">
+        <v>371</v>
+      </c>
+      <c r="H9" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8">
+      <c r="B10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" t="s">
+        <v>380</v>
+      </c>
+      <c r="D10" t="s">
+        <v>381</v>
+      </c>
+      <c r="E10" t="s">
+        <v>25</v>
+      </c>
+      <c r="F10" t="s">
+        <v>35</v>
+      </c>
+      <c r="G10" t="s">
+        <v>371</v>
+      </c>
+      <c r="H10" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="11" spans="2:8">
+      <c r="B11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" t="s">
+        <v>382</v>
+      </c>
+      <c r="D11" t="s">
+        <v>383</v>
+      </c>
+      <c r="E11" t="s">
+        <v>25</v>
+      </c>
+      <c r="F11" t="s">
+        <v>35</v>
+      </c>
+      <c r="G11" t="s">
+        <v>371</v>
+      </c>
+      <c r="H11" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="12" spans="2:8">
+      <c r="B12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" t="s">
+        <v>384</v>
+      </c>
+      <c r="D12" t="s">
+        <v>385</v>
+      </c>
+      <c r="E12" t="s">
+        <v>25</v>
+      </c>
+      <c r="F12" t="s">
+        <v>35</v>
+      </c>
+      <c r="G12" t="s">
+        <v>371</v>
+      </c>
+      <c r="H12" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8">
+      <c r="B13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" t="s">
+        <v>386</v>
+      </c>
+      <c r="D13" t="s">
+        <v>387</v>
+      </c>
+      <c r="E13" t="s">
+        <v>25</v>
+      </c>
+      <c r="F13" t="s">
+        <v>35</v>
+      </c>
+      <c r="G13" t="s">
+        <v>371</v>
+      </c>
+      <c r="H13" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="14" spans="2:8">
+      <c r="B14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" t="s">
+        <v>388</v>
+      </c>
+      <c r="D14" t="s">
+        <v>389</v>
+      </c>
+      <c r="E14" t="s">
+        <v>25</v>
+      </c>
+      <c r="F14" t="s">
+        <v>35</v>
+      </c>
+      <c r="G14" t="s">
+        <v>371</v>
+      </c>
+      <c r="H14" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="15" spans="2:8">
+      <c r="B15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" t="s">
+        <v>390</v>
+      </c>
+      <c r="D15" t="s">
+        <v>391</v>
+      </c>
+      <c r="E15" t="s">
+        <v>25</v>
+      </c>
+      <c r="F15" t="s">
+        <v>35</v>
+      </c>
+      <c r="G15" t="s">
+        <v>371</v>
+      </c>
+      <c r="H15" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="16" spans="2:8">
+      <c r="B16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" t="s">
+        <v>392</v>
+      </c>
+      <c r="D16" t="s">
+        <v>393</v>
+      </c>
+      <c r="E16" t="s">
+        <v>25</v>
+      </c>
+      <c r="F16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G16" t="s">
+        <v>371</v>
+      </c>
+      <c r="H16" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8">
+      <c r="B17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" t="s">
+        <v>394</v>
+      </c>
+      <c r="D17" t="s">
+        <v>395</v>
+      </c>
+      <c r="E17" t="s">
+        <v>25</v>
+      </c>
+      <c r="F17" t="s">
+        <v>35</v>
+      </c>
+      <c r="G17" t="s">
+        <v>371</v>
+      </c>
+      <c r="H17" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8">
+      <c r="B18" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" t="s">
+        <v>396</v>
+      </c>
+      <c r="D18" t="s">
+        <v>397</v>
+      </c>
+      <c r="E18" t="s">
+        <v>25</v>
+      </c>
+      <c r="F18" t="s">
+        <v>35</v>
+      </c>
+      <c r="G18" t="s">
+        <v>371</v>
+      </c>
+      <c r="H18" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8">
+      <c r="B19" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" t="s">
+        <v>398</v>
+      </c>
+      <c r="D19" t="s">
+        <v>399</v>
+      </c>
+      <c r="E19" t="s">
+        <v>25</v>
+      </c>
+      <c r="F19" t="s">
+        <v>35</v>
+      </c>
+      <c r="G19" t="s">
+        <v>371</v>
+      </c>
+      <c r="H19" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8">
+      <c r="B20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20" t="s">
+        <v>400</v>
+      </c>
+      <c r="D20" t="s">
+        <v>401</v>
+      </c>
+      <c r="E20" t="s">
+        <v>25</v>
+      </c>
+      <c r="F20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G20" t="s">
+        <v>371</v>
+      </c>
+      <c r="H20" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8">
+      <c r="B21" t="s">
+        <v>17</v>
+      </c>
+      <c r="C21" t="s">
+        <v>402</v>
+      </c>
+      <c r="D21" t="s">
+        <v>403</v>
+      </c>
+      <c r="E21" t="s">
+        <v>25</v>
+      </c>
+      <c r="F21" t="s">
+        <v>35</v>
+      </c>
+      <c r="G21" t="s">
+        <v>371</v>
+      </c>
+      <c r="H21" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8">
+      <c r="B22" t="s">
+        <v>17</v>
+      </c>
+      <c r="C22" t="s">
+        <v>404</v>
+      </c>
+      <c r="D22" t="s">
+        <v>405</v>
+      </c>
+      <c r="E22" t="s">
+        <v>25</v>
+      </c>
+      <c r="F22" t="s">
+        <v>35</v>
+      </c>
+      <c r="G22" t="s">
+        <v>371</v>
+      </c>
+      <c r="H22" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8">
+      <c r="B23" t="s">
+        <v>17</v>
+      </c>
+      <c r="C23" t="s">
+        <v>406</v>
+      </c>
+      <c r="D23" t="s">
+        <v>407</v>
+      </c>
+      <c r="E23" t="s">
+        <v>25</v>
+      </c>
+      <c r="F23" t="s">
+        <v>35</v>
+      </c>
+      <c r="G23" t="s">
+        <v>371</v>
+      </c>
+      <c r="H23" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8">
+      <c r="B24" t="s">
+        <v>17</v>
+      </c>
+      <c r="C24" t="s">
+        <v>408</v>
+      </c>
+      <c r="D24" t="s">
+        <v>409</v>
+      </c>
+      <c r="E24" t="s">
+        <v>25</v>
+      </c>
+      <c r="F24" t="s">
+        <v>35</v>
+      </c>
+      <c r="G24" t="s">
+        <v>371</v>
+      </c>
+      <c r="H24" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8">
+      <c r="B25" t="s">
+        <v>17</v>
+      </c>
+      <c r="C25" t="s">
+        <v>410</v>
+      </c>
+      <c r="D25" t="s">
+        <v>411</v>
+      </c>
+      <c r="E25" t="s">
+        <v>25</v>
+      </c>
+      <c r="F25" t="s">
+        <v>35</v>
+      </c>
+      <c r="G25" t="s">
+        <v>371</v>
+      </c>
+      <c r="H25" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="26" spans="2:8">
+      <c r="B26" t="s">
+        <v>17</v>
+      </c>
+      <c r="C26" t="s">
+        <v>412</v>
+      </c>
+      <c r="D26" t="s">
+        <v>413</v>
+      </c>
+      <c r="E26" t="s">
+        <v>25</v>
+      </c>
+      <c r="F26" t="s">
+        <v>35</v>
+      </c>
+      <c r="G26" t="s">
+        <v>371</v>
+      </c>
+      <c r="H26" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8">
+      <c r="B27" t="s">
+        <v>17</v>
+      </c>
+      <c r="C27" t="s">
+        <v>414</v>
+      </c>
+      <c r="D27" t="s">
+        <v>415</v>
+      </c>
+      <c r="E27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F27" t="s">
+        <v>35</v>
+      </c>
+      <c r="G27" t="s">
+        <v>371</v>
+      </c>
+      <c r="H27" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="28" spans="2:8">
+      <c r="B28" t="s">
+        <v>17</v>
+      </c>
+      <c r="C28" t="s">
+        <v>416</v>
+      </c>
+      <c r="D28" t="s">
+        <v>417</v>
+      </c>
+      <c r="E28" t="s">
+        <v>25</v>
+      </c>
+      <c r="F28" t="s">
+        <v>35</v>
+      </c>
+      <c r="G28" t="s">
+        <v>371</v>
+      </c>
+      <c r="H28" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="29" spans="2:8">
+      <c r="B29" t="s">
+        <v>17</v>
+      </c>
+      <c r="C29" t="s">
+        <v>418</v>
+      </c>
+      <c r="D29" t="s">
+        <v>419</v>
+      </c>
+      <c r="E29" t="s">
+        <v>25</v>
+      </c>
+      <c r="F29" t="s">
+        <v>35</v>
+      </c>
+      <c r="G29" t="s">
+        <v>371</v>
+      </c>
+      <c r="H29" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="30" spans="2:8">
+      <c r="B30" t="s">
+        <v>17</v>
+      </c>
+      <c r="C30" t="s">
+        <v>420</v>
+      </c>
+      <c r="D30" t="s">
+        <v>421</v>
+      </c>
+      <c r="E30" t="s">
+        <v>25</v>
+      </c>
+      <c r="F30" t="s">
+        <v>35</v>
+      </c>
+      <c r="G30" t="s">
+        <v>371</v>
+      </c>
+      <c r="H30" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="31" spans="2:8">
+      <c r="B31" t="s">
+        <v>17</v>
+      </c>
+      <c r="C31" t="s">
+        <v>422</v>
+      </c>
+      <c r="D31" t="s">
+        <v>423</v>
+      </c>
+      <c r="E31" t="s">
+        <v>25</v>
+      </c>
+      <c r="F31" t="s">
+        <v>35</v>
+      </c>
+      <c r="G31" t="s">
+        <v>371</v>
+      </c>
+      <c r="H31" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="32" spans="2:8">
+      <c r="B32" t="s">
+        <v>17</v>
+      </c>
+      <c r="C32" t="s">
+        <v>424</v>
+      </c>
+      <c r="D32" t="s">
+        <v>425</v>
+      </c>
+      <c r="E32" t="s">
+        <v>25</v>
+      </c>
+      <c r="F32" t="s">
+        <v>35</v>
+      </c>
+      <c r="G32" t="s">
+        <v>371</v>
+      </c>
+      <c r="H32" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="33" spans="2:8">
+      <c r="B33" t="s">
+        <v>17</v>
+      </c>
+      <c r="C33" t="s">
+        <v>426</v>
+      </c>
+      <c r="D33" t="s">
+        <v>427</v>
+      </c>
+      <c r="E33" t="s">
+        <v>25</v>
+      </c>
+      <c r="F33" t="s">
+        <v>35</v>
+      </c>
+      <c r="G33" t="s">
+        <v>371</v>
+      </c>
+      <c r="H33" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="34" spans="2:8">
+      <c r="B34" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34" t="s">
+        <v>428</v>
+      </c>
+      <c r="D34" t="s">
+        <v>429</v>
+      </c>
+      <c r="E34" t="s">
+        <v>25</v>
+      </c>
+      <c r="F34" t="s">
+        <v>35</v>
+      </c>
+      <c r="G34" t="s">
+        <v>371</v>
+      </c>
+      <c r="H34" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="35" spans="2:8">
+      <c r="B35" t="s">
+        <v>17</v>
+      </c>
+      <c r="C35" t="s">
+        <v>430</v>
+      </c>
+      <c r="D35" t="s">
+        <v>431</v>
+      </c>
+      <c r="E35" t="s">
+        <v>25</v>
+      </c>
+      <c r="F35" t="s">
+        <v>35</v>
+      </c>
+      <c r="G35" t="s">
+        <v>371</v>
+      </c>
+      <c r="H35" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="36" spans="2:8">
+      <c r="B36" t="s">
+        <v>17</v>
+      </c>
+      <c r="C36" t="s">
+        <v>432</v>
+      </c>
+      <c r="D36" t="s">
+        <v>433</v>
+      </c>
+      <c r="E36" t="s">
+        <v>25</v>
+      </c>
+      <c r="F36" t="s">
+        <v>35</v>
+      </c>
+      <c r="G36" t="s">
+        <v>371</v>
+      </c>
+      <c r="H36" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="37" spans="2:8">
+      <c r="B37" t="s">
+        <v>17</v>
+      </c>
+      <c r="C37" t="s">
+        <v>434</v>
+      </c>
+      <c r="D37" t="s">
+        <v>435</v>
+      </c>
+      <c r="E37" t="s">
+        <v>25</v>
+      </c>
+      <c r="F37" t="s">
+        <v>35</v>
+      </c>
+      <c r="G37" t="s">
+        <v>371</v>
+      </c>
+      <c r="H37" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="38" spans="2:8">
+      <c r="B38" t="s">
+        <v>17</v>
+      </c>
+      <c r="C38" t="s">
+        <v>436</v>
+      </c>
+      <c r="D38" t="s">
+        <v>437</v>
+      </c>
+      <c r="E38" t="s">
+        <v>25</v>
+      </c>
+      <c r="F38" t="s">
+        <v>35</v>
+      </c>
+      <c r="G38" t="s">
+        <v>371</v>
+      </c>
+      <c r="H38" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="39" spans="2:8">
+      <c r="B39" t="s">
+        <v>17</v>
+      </c>
+      <c r="C39" t="s">
+        <v>438</v>
+      </c>
+      <c r="D39" t="s">
+        <v>439</v>
+      </c>
+      <c r="E39" t="s">
+        <v>25</v>
+      </c>
+      <c r="F39" t="s">
+        <v>35</v>
+      </c>
+      <c r="G39" t="s">
+        <v>371</v>
+      </c>
+      <c r="H39" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="40" spans="2:8">
+      <c r="B40" t="s">
+        <v>17</v>
+      </c>
+      <c r="C40" t="s">
+        <v>440</v>
+      </c>
+      <c r="D40" t="s">
+        <v>441</v>
+      </c>
+      <c r="E40" t="s">
+        <v>25</v>
+      </c>
+      <c r="F40" t="s">
+        <v>35</v>
+      </c>
+      <c r="G40" t="s">
+        <v>371</v>
+      </c>
+      <c r="H40" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="41" spans="2:8">
+      <c r="B41" t="s">
+        <v>17</v>
+      </c>
+      <c r="C41" t="s">
+        <v>442</v>
+      </c>
+      <c r="D41" t="s">
+        <v>443</v>
+      </c>
+      <c r="E41" t="s">
+        <v>25</v>
+      </c>
+      <c r="F41" t="s">
+        <v>35</v>
+      </c>
+      <c r="G41" t="s">
+        <v>371</v>
+      </c>
+      <c r="H41" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="42" spans="2:8">
+      <c r="B42" t="s">
+        <v>17</v>
+      </c>
+      <c r="C42" t="s">
+        <v>444</v>
+      </c>
+      <c r="D42" t="s">
+        <v>445</v>
+      </c>
+      <c r="E42" t="s">
+        <v>25</v>
+      </c>
+      <c r="F42" t="s">
+        <v>35</v>
+      </c>
+      <c r="G42" t="s">
+        <v>371</v>
+      </c>
+      <c r="H42" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="43" spans="2:8">
+      <c r="B43" t="s">
+        <v>17</v>
+      </c>
+      <c r="C43" t="s">
+        <v>446</v>
+      </c>
+      <c r="D43" t="s">
+        <v>447</v>
+      </c>
+      <c r="E43" t="s">
+        <v>25</v>
+      </c>
+      <c r="F43" t="s">
+        <v>35</v>
+      </c>
+      <c r="G43" t="s">
+        <v>371</v>
+      </c>
+      <c r="H43" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="44" spans="2:8">
+      <c r="B44" t="s">
+        <v>17</v>
+      </c>
+      <c r="C44" t="s">
+        <v>448</v>
+      </c>
+      <c r="D44" t="s">
+        <v>449</v>
+      </c>
+      <c r="E44" t="s">
+        <v>25</v>
+      </c>
+      <c r="F44" t="s">
+        <v>35</v>
+      </c>
+      <c r="G44" t="s">
+        <v>371</v>
+      </c>
+      <c r="H44" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="45" spans="2:8">
+      <c r="B45" t="s">
+        <v>17</v>
+      </c>
+      <c r="C45" t="s">
+        <v>450</v>
+      </c>
+      <c r="D45" t="s">
+        <v>451</v>
+      </c>
+      <c r="E45" t="s">
+        <v>25</v>
+      </c>
+      <c r="F45" t="s">
+        <v>35</v>
+      </c>
+      <c r="G45" t="s">
+        <v>371</v>
+      </c>
+      <c r="H45" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="46" spans="2:8">
+      <c r="B46" t="s">
+        <v>17</v>
+      </c>
+      <c r="C46" t="s">
+        <v>452</v>
+      </c>
+      <c r="D46" t="s">
+        <v>453</v>
+      </c>
+      <c r="E46" t="s">
+        <v>25</v>
+      </c>
+      <c r="F46" t="s">
+        <v>35</v>
+      </c>
+      <c r="G46" t="s">
+        <v>371</v>
+      </c>
+      <c r="H46" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="47" spans="2:8">
+      <c r="B47" t="s">
+        <v>17</v>
+      </c>
+      <c r="C47" t="s">
+        <v>454</v>
+      </c>
+      <c r="D47" t="s">
+        <v>455</v>
+      </c>
+      <c r="E47" t="s">
+        <v>25</v>
+      </c>
+      <c r="F47" t="s">
+        <v>35</v>
+      </c>
+      <c r="G47" t="s">
+        <v>371</v>
+      </c>
+      <c r="H47" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="48" spans="2:8">
+      <c r="B48" t="s">
+        <v>17</v>
+      </c>
+      <c r="C48" t="s">
+        <v>456</v>
+      </c>
+      <c r="D48" t="s">
+        <v>457</v>
+      </c>
+      <c r="E48" t="s">
+        <v>25</v>
+      </c>
+      <c r="F48" t="s">
+        <v>35</v>
+      </c>
+      <c r="G48" t="s">
+        <v>371</v>
+      </c>
+      <c r="H48" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="49" spans="2:8">
+      <c r="B49" t="s">
+        <v>17</v>
+      </c>
+      <c r="C49" t="s">
+        <v>458</v>
+      </c>
+      <c r="D49" t="s">
+        <v>459</v>
+      </c>
+      <c r="E49" t="s">
+        <v>25</v>
+      </c>
+      <c r="F49" t="s">
+        <v>35</v>
+      </c>
+      <c r="G49" t="s">
+        <v>371</v>
+      </c>
+      <c r="H49" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="50" spans="2:8">
+      <c r="B50" t="s">
+        <v>17</v>
+      </c>
+      <c r="C50" t="s">
+        <v>460</v>
+      </c>
+      <c r="D50" t="s">
+        <v>461</v>
+      </c>
+      <c r="E50" t="s">
+        <v>25</v>
+      </c>
+      <c r="F50" t="s">
+        <v>35</v>
+      </c>
+      <c r="G50" t="s">
+        <v>371</v>
+      </c>
+      <c r="H50" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="51" spans="2:8">
+      <c r="B51" t="s">
+        <v>17</v>
+      </c>
+      <c r="C51" t="s">
+        <v>462</v>
+      </c>
+      <c r="D51" t="s">
+        <v>463</v>
+      </c>
+      <c r="E51" t="s">
+        <v>25</v>
+      </c>
+      <c r="F51" t="s">
+        <v>35</v>
+      </c>
+      <c r="G51" t="s">
+        <v>371</v>
+      </c>
+      <c r="H51" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="52" spans="2:8">
+      <c r="B52" t="s">
+        <v>17</v>
+      </c>
+      <c r="C52" t="s">
+        <v>464</v>
+      </c>
+      <c r="D52" t="s">
+        <v>465</v>
+      </c>
+      <c r="E52" t="s">
+        <v>25</v>
+      </c>
+      <c r="F52" t="s">
+        <v>35</v>
+      </c>
+      <c r="G52" t="s">
+        <v>371</v>
+      </c>
+      <c r="H52" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="53" spans="2:8">
+      <c r="B53" t="s">
+        <v>17</v>
+      </c>
+      <c r="C53" t="s">
+        <v>466</v>
+      </c>
+      <c r="D53" t="s">
+        <v>467</v>
+      </c>
+      <c r="E53" t="s">
+        <v>25</v>
+      </c>
+      <c r="F53" t="s">
+        <v>35</v>
+      </c>
+      <c r="G53" t="s">
+        <v>371</v>
+      </c>
+      <c r="H53" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="54" spans="2:8">
+      <c r="B54" t="s">
+        <v>17</v>
+      </c>
+      <c r="C54" t="s">
+        <v>468</v>
+      </c>
+      <c r="D54" t="s">
+        <v>469</v>
+      </c>
+      <c r="E54" t="s">
+        <v>25</v>
+      </c>
+      <c r="F54" t="s">
+        <v>35</v>
+      </c>
+      <c r="G54" t="s">
+        <v>371</v>
+      </c>
+      <c r="H54" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="55" spans="2:8">
+      <c r="B55" t="s">
+        <v>17</v>
+      </c>
+      <c r="C55" t="s">
+        <v>470</v>
+      </c>
+      <c r="D55" t="s">
+        <v>471</v>
+      </c>
+      <c r="E55" t="s">
+        <v>25</v>
+      </c>
+      <c r="F55" t="s">
+        <v>35</v>
+      </c>
+      <c r="G55" t="s">
+        <v>371</v>
+      </c>
+      <c r="H55" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="56" spans="2:8">
+      <c r="B56" t="s">
+        <v>17</v>
+      </c>
+      <c r="C56" t="s">
+        <v>472</v>
+      </c>
+      <c r="D56" t="s">
+        <v>473</v>
+      </c>
+      <c r="E56" t="s">
+        <v>25</v>
+      </c>
+      <c r="F56" t="s">
+        <v>35</v>
+      </c>
+      <c r="G56" t="s">
+        <v>371</v>
+      </c>
+      <c r="H56" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="57" spans="2:8">
+      <c r="B57" t="s">
+        <v>17</v>
+      </c>
+      <c r="C57" t="s">
+        <v>474</v>
+      </c>
+      <c r="D57" t="s">
+        <v>475</v>
+      </c>
+      <c r="E57" t="s">
+        <v>25</v>
+      </c>
+      <c r="F57" t="s">
+        <v>35</v>
+      </c>
+      <c r="G57" t="s">
+        <v>371</v>
+      </c>
+      <c r="H57" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="58" spans="2:8">
+      <c r="B58" t="s">
+        <v>17</v>
+      </c>
+      <c r="C58" t="s">
+        <v>476</v>
+      </c>
+      <c r="D58" t="s">
+        <v>477</v>
+      </c>
+      <c r="E58" t="s">
+        <v>25</v>
+      </c>
+      <c r="F58" t="s">
+        <v>35</v>
+      </c>
+      <c r="G58" t="s">
+        <v>371</v>
+      </c>
+      <c r="H58" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="59" spans="2:8">
+      <c r="B59" t="s">
+        <v>17</v>
+      </c>
+      <c r="C59" t="s">
+        <v>478</v>
+      </c>
+      <c r="D59" t="s">
+        <v>479</v>
+      </c>
+      <c r="E59" t="s">
+        <v>25</v>
+      </c>
+      <c r="F59" t="s">
+        <v>35</v>
+      </c>
+      <c r="G59" t="s">
+        <v>371</v>
+      </c>
+      <c r="H59" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="60" spans="2:8">
+      <c r="B60" t="s">
+        <v>17</v>
+      </c>
+      <c r="C60" t="s">
+        <v>480</v>
+      </c>
+      <c r="D60" t="s">
+        <v>481</v>
+      </c>
+      <c r="E60" t="s">
+        <v>25</v>
+      </c>
+      <c r="F60" t="s">
+        <v>35</v>
+      </c>
+      <c r="G60" t="s">
+        <v>371</v>
+      </c>
+      <c r="H60" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="61" spans="2:8">
+      <c r="B61" t="s">
+        <v>17</v>
+      </c>
+      <c r="C61" t="s">
+        <v>482</v>
+      </c>
+      <c r="D61" t="s">
+        <v>483</v>
+      </c>
+      <c r="E61" t="s">
+        <v>25</v>
+      </c>
+      <c r="F61" t="s">
+        <v>35</v>
+      </c>
+      <c r="G61" t="s">
+        <v>371</v>
+      </c>
+      <c r="H61" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="62" spans="2:8">
+      <c r="B62" t="s">
+        <v>17</v>
+      </c>
+      <c r="C62" t="s">
+        <v>484</v>
+      </c>
+      <c r="D62" t="s">
+        <v>485</v>
+      </c>
+      <c r="E62" t="s">
+        <v>25</v>
+      </c>
+      <c r="F62" t="s">
+        <v>35</v>
+      </c>
+      <c r="G62" t="s">
+        <v>371</v>
+      </c>
+      <c r="H62" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="63" spans="2:8">
+      <c r="B63" t="s">
+        <v>17</v>
+      </c>
+      <c r="C63" t="s">
+        <v>486</v>
+      </c>
+      <c r="D63" t="s">
+        <v>487</v>
+      </c>
+      <c r="E63" t="s">
+        <v>25</v>
+      </c>
+      <c r="F63" t="s">
+        <v>35</v>
+      </c>
+      <c r="G63" t="s">
+        <v>371</v>
+      </c>
+      <c r="H63" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="64" spans="2:8">
+      <c r="B64" t="s">
+        <v>17</v>
+      </c>
+      <c r="C64" t="s">
+        <v>488</v>
+      </c>
+      <c r="D64" t="s">
+        <v>489</v>
+      </c>
+      <c r="E64" t="s">
+        <v>25</v>
+      </c>
+      <c r="F64" t="s">
+        <v>35</v>
+      </c>
+      <c r="G64" t="s">
+        <v>371</v>
+      </c>
+      <c r="H64" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="65" spans="2:8">
+      <c r="B65" t="s">
+        <v>17</v>
+      </c>
+      <c r="C65" t="s">
+        <v>490</v>
+      </c>
+      <c r="D65" t="s">
+        <v>491</v>
+      </c>
+      <c r="E65" t="s">
+        <v>25</v>
+      </c>
+      <c r="F65" t="s">
+        <v>35</v>
+      </c>
+      <c r="G65" t="s">
+        <v>371</v>
+      </c>
+      <c r="H65" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="66" spans="2:8">
+      <c r="B66" t="s">
+        <v>17</v>
+      </c>
+      <c r="C66" t="s">
+        <v>492</v>
+      </c>
+      <c r="D66" t="s">
+        <v>493</v>
+      </c>
+      <c r="E66" t="s">
+        <v>25</v>
+      </c>
+      <c r="F66" t="s">
+        <v>35</v>
+      </c>
+      <c r="G66" t="s">
+        <v>371</v>
+      </c>
+      <c r="H66" t="s">
+        <v>223</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2F298A9-BCD9-4ABF-BE3B-9D1BDD3E7001}">
   <dimension ref="B3:R77"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
@@ -3994,7 +5458,7 @@
         <v>16</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="N4" s="5" t="s">
         <v>10</v>
@@ -4026,10 +5490,10 @@
         <v>17</v>
       </c>
       <c r="N5" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="O5" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="P5" t="s">
         <v>25</v>
@@ -4038,7 +5502,7 @@
         <v>35</v>
       </c>
       <c r="R5" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="6" spans="2:18">
@@ -4055,10 +5519,10 @@
         <v>17</v>
       </c>
       <c r="N6" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="O6" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="P6" t="s">
         <v>25</v>
@@ -4067,7 +5531,7 @@
         <v>35</v>
       </c>
       <c r="R6" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="7" spans="2:18">
@@ -4084,10 +5548,10 @@
         <v>17</v>
       </c>
       <c r="N7" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="O7" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="P7" t="s">
         <v>25</v>
@@ -4096,7 +5560,7 @@
         <v>35</v>
       </c>
       <c r="R7" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="8" spans="2:18">
@@ -4113,10 +5577,10 @@
         <v>17</v>
       </c>
       <c r="N8" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="O8" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="P8" t="s">
         <v>25</v>
@@ -4125,7 +5589,7 @@
         <v>35</v>
       </c>
       <c r="R8" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="9" spans="2:18">
@@ -4142,10 +5606,10 @@
         <v>17</v>
       </c>
       <c r="N9" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="O9" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="P9" t="s">
         <v>25</v>
@@ -4154,7 +5618,7 @@
         <v>35</v>
       </c>
       <c r="R9" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="10" spans="2:18">
@@ -4171,10 +5635,10 @@
         <v>17</v>
       </c>
       <c r="N10" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="O10" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="P10" t="s">
         <v>25</v>
@@ -4183,7 +5647,7 @@
         <v>35</v>
       </c>
       <c r="R10" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="11" spans="2:18">
@@ -4200,10 +5664,10 @@
         <v>17</v>
       </c>
       <c r="N11" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="O11" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="P11" t="s">
         <v>25</v>
@@ -4212,7 +5676,7 @@
         <v>35</v>
       </c>
       <c r="R11" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="12" spans="2:18">
@@ -4229,10 +5693,10 @@
         <v>17</v>
       </c>
       <c r="N12" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="O12" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="P12" t="s">
         <v>25</v>
@@ -4241,7 +5705,7 @@
         <v>35</v>
       </c>
       <c r="R12" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="13" spans="2:18">
@@ -4258,10 +5722,10 @@
         <v>17</v>
       </c>
       <c r="N13" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="O13" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="P13" t="s">
         <v>25</v>
@@ -4270,7 +5734,7 @@
         <v>35</v>
       </c>
       <c r="R13" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="14" spans="2:18">
@@ -4290,10 +5754,10 @@
         <v>17</v>
       </c>
       <c r="N14" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="O14" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="P14" t="s">
         <v>25</v>
@@ -4302,7 +5766,7 @@
         <v>35</v>
       </c>
       <c r="R14" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="15" spans="2:18">
@@ -4322,10 +5786,10 @@
         <v>17</v>
       </c>
       <c r="N15" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="O15" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="P15" t="s">
         <v>25</v>
@@ -4334,7 +5798,7 @@
         <v>35</v>
       </c>
       <c r="R15" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="16" spans="2:18">
@@ -4363,10 +5827,10 @@
         <v>17</v>
       </c>
       <c r="N16" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="O16" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="P16" t="s">
         <v>25</v>
@@ -4375,7 +5839,7 @@
         <v>35</v>
       </c>
       <c r="R16" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="17" spans="2:18">
@@ -4395,10 +5859,10 @@
         <v>17</v>
       </c>
       <c r="N17" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="O17" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="P17" t="s">
         <v>25</v>
@@ -4407,7 +5871,7 @@
         <v>35</v>
       </c>
       <c r="R17" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="18" spans="2:18">
@@ -4427,10 +5891,10 @@
         <v>17</v>
       </c>
       <c r="N18" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="O18" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="P18" t="s">
         <v>25</v>
@@ -4439,7 +5903,7 @@
         <v>35</v>
       </c>
       <c r="R18" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="19" spans="2:18">
@@ -4459,10 +5923,10 @@
         <v>17</v>
       </c>
       <c r="N19" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="O19" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="P19" t="s">
         <v>25</v>
@@ -4471,7 +5935,7 @@
         <v>35</v>
       </c>
       <c r="R19" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="20" spans="2:18">
@@ -4491,10 +5955,10 @@
         <v>17</v>
       </c>
       <c r="N20" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="O20" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="P20" t="s">
         <v>25</v>
@@ -4503,7 +5967,7 @@
         <v>35</v>
       </c>
       <c r="R20" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="21" spans="2:18">
@@ -4529,10 +5993,10 @@
         <v>17</v>
       </c>
       <c r="N21" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="O21" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="P21" t="s">
         <v>25</v>
@@ -4541,7 +6005,7 @@
         <v>35</v>
       </c>
       <c r="R21" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="22" spans="2:18">
@@ -4561,10 +6025,10 @@
         <v>17</v>
       </c>
       <c r="N22" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="O22" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="P22" t="s">
         <v>25</v>
@@ -4573,7 +6037,7 @@
         <v>35</v>
       </c>
       <c r="R22" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="23" spans="2:18">
@@ -4590,10 +6054,10 @@
         <v>17</v>
       </c>
       <c r="N23" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="O23" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="P23" t="s">
         <v>25</v>
@@ -4602,7 +6066,7 @@
         <v>35</v>
       </c>
       <c r="R23" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="24" spans="2:18">
@@ -4619,10 +6083,10 @@
         <v>17</v>
       </c>
       <c r="N24" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="O24" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="P24" t="s">
         <v>25</v>
@@ -4631,7 +6095,7 @@
         <v>35</v>
       </c>
       <c r="R24" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="25" spans="2:18">
@@ -4639,10 +6103,10 @@
         <v>17</v>
       </c>
       <c r="N25" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="O25" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="P25" t="s">
         <v>25</v>
@@ -4651,7 +6115,7 @@
         <v>35</v>
       </c>
       <c r="R25" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="26" spans="2:18">
@@ -4659,10 +6123,10 @@
         <v>17</v>
       </c>
       <c r="N26" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="O26" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="P26" t="s">
         <v>25</v>
@@ -4671,99 +6135,101 @@
         <v>35</v>
       </c>
       <c r="R26" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="27" spans="2:18">
+      <c r="M27" t="s">
+        <v>17</v>
+      </c>
+      <c r="N27" t="s">
+        <v>266</v>
+      </c>
+      <c r="O27" t="s">
+        <v>267</v>
+      </c>
+      <c r="P27" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>35</v>
+      </c>
+      <c r="R27" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="28" spans="2:18" ht="17.649999999999999" thickBot="1">
+      <c r="B28" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="M28" t="s">
+        <v>17</v>
+      </c>
+      <c r="N28" t="s">
+        <v>268</v>
+      </c>
+      <c r="O28" t="s">
+        <v>269</v>
+      </c>
+      <c r="P28" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>35</v>
+      </c>
+      <c r="R28" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="29" spans="2:18" ht="15" thickTop="1" thickBot="1">
+      <c r="B29" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="M29" t="s">
+        <v>17</v>
+      </c>
+      <c r="N29" t="s">
+        <v>270</v>
+      </c>
+      <c r="O29" t="s">
+        <v>271</v>
+      </c>
+      <c r="P29" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>35</v>
+      </c>
+      <c r="R29" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="30" spans="2:18">
+      <c r="B30" t="s">
+        <v>218</v>
+      </c>
+      <c r="C30" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="27" spans="2:18">
-      <c r="B27" t="s">
-        <v>488</v>
-      </c>
-      <c r="M27" t="s">
-        <v>17</v>
-      </c>
-      <c r="N27" t="s">
-        <v>260</v>
-      </c>
-      <c r="O27" t="s">
-        <v>261</v>
-      </c>
-      <c r="P27" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q27" t="s">
-        <v>35</v>
-      </c>
-      <c r="R27" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="28" spans="2:18">
-      <c r="B28" t="s">
-        <v>173</v>
-      </c>
-      <c r="C28" t="s">
-        <v>489</v>
-      </c>
-      <c r="D28" t="s">
-        <v>490</v>
-      </c>
-      <c r="M28" t="s">
-        <v>17</v>
-      </c>
-      <c r="N28" t="s">
-        <v>262</v>
-      </c>
-      <c r="O28" t="s">
-        <v>263</v>
-      </c>
-      <c r="P28" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q28" t="s">
-        <v>35</v>
-      </c>
-      <c r="R28" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="29" spans="2:18">
-      <c r="B29" t="s">
-        <v>493</v>
-      </c>
-      <c r="C29" t="s">
-        <v>492</v>
-      </c>
-      <c r="D29" t="s">
-        <v>491</v>
-      </c>
-      <c r="M29" t="s">
-        <v>17</v>
-      </c>
-      <c r="N29" t="s">
-        <v>264</v>
-      </c>
-      <c r="O29" t="s">
-        <v>265</v>
-      </c>
-      <c r="P29" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q29" t="s">
-        <v>35</v>
-      </c>
-      <c r="R29" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="30" spans="2:18">
+      <c r="D30" t="s">
+        <v>216</v>
+      </c>
       <c r="M30" t="s">
         <v>17</v>
       </c>
       <c r="N30" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="O30" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="P30" t="s">
         <v>25</v>
@@ -4772,7 +6238,7 @@
         <v>35</v>
       </c>
       <c r="R30" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="31" spans="2:18">
@@ -4780,10 +6246,10 @@
         <v>17</v>
       </c>
       <c r="N31" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="O31" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="P31" t="s">
         <v>25</v>
@@ -4792,7 +6258,7 @@
         <v>35</v>
       </c>
       <c r="R31" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="32" spans="2:18">
@@ -4800,10 +6266,10 @@
         <v>17</v>
       </c>
       <c r="N32" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="O32" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="P32" t="s">
         <v>25</v>
@@ -4812,7 +6278,7 @@
         <v>35</v>
       </c>
       <c r="R32" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="33" spans="13:18">
@@ -4820,10 +6286,10 @@
         <v>17</v>
       </c>
       <c r="N33" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="O33" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="P33" t="s">
         <v>25</v>
@@ -4832,7 +6298,7 @@
         <v>35</v>
       </c>
       <c r="R33" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="34" spans="13:18">
@@ -4840,10 +6306,10 @@
         <v>17</v>
       </c>
       <c r="N34" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="O34" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="P34" t="s">
         <v>25</v>
@@ -4852,7 +6318,7 @@
         <v>35</v>
       </c>
       <c r="R34" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="35" spans="13:18">
@@ -4860,10 +6326,10 @@
         <v>17</v>
       </c>
       <c r="N35" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="O35" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="P35" t="s">
         <v>25</v>
@@ -4872,7 +6338,7 @@
         <v>35</v>
       </c>
       <c r="R35" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="36" spans="13:18">
@@ -4880,10 +6346,10 @@
         <v>17</v>
       </c>
       <c r="N36" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="O36" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="P36" t="s">
         <v>25</v>
@@ -4892,7 +6358,7 @@
         <v>35</v>
       </c>
       <c r="R36" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="37" spans="13:18">
@@ -4900,10 +6366,10 @@
         <v>17</v>
       </c>
       <c r="N37" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="O37" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="P37" t="s">
         <v>25</v>
@@ -4912,7 +6378,7 @@
         <v>35</v>
       </c>
       <c r="R37" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="38" spans="13:18">
@@ -4920,10 +6386,10 @@
         <v>17</v>
       </c>
       <c r="N38" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="O38" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="P38" t="s">
         <v>25</v>
@@ -4932,7 +6398,7 @@
         <v>35</v>
       </c>
       <c r="R38" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="39" spans="13:18">
@@ -4940,10 +6406,10 @@
         <v>17</v>
       </c>
       <c r="N39" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="O39" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="P39" t="s">
         <v>25</v>
@@ -4952,7 +6418,7 @@
         <v>35</v>
       </c>
       <c r="R39" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="40" spans="13:18">
@@ -4960,10 +6426,10 @@
         <v>17</v>
       </c>
       <c r="N40" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="O40" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="P40" t="s">
         <v>25</v>
@@ -4972,7 +6438,7 @@
         <v>35</v>
       </c>
       <c r="R40" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="41" spans="13:18">
@@ -4980,10 +6446,10 @@
         <v>17</v>
       </c>
       <c r="N41" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="O41" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="P41" t="s">
         <v>25</v>
@@ -4992,7 +6458,7 @@
         <v>35</v>
       </c>
       <c r="R41" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="42" spans="13:18">
@@ -5000,10 +6466,10 @@
         <v>17</v>
       </c>
       <c r="N42" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="O42" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="P42" t="s">
         <v>25</v>
@@ -5012,7 +6478,7 @@
         <v>35</v>
       </c>
       <c r="R42" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="43" spans="13:18">
@@ -5020,10 +6486,10 @@
         <v>17</v>
       </c>
       <c r="N43" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="O43" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="P43" t="s">
         <v>25</v>
@@ -5032,7 +6498,7 @@
         <v>35</v>
       </c>
       <c r="R43" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="44" spans="13:18">
@@ -5040,10 +6506,10 @@
         <v>17</v>
       </c>
       <c r="N44" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="O44" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="P44" t="s">
         <v>25</v>
@@ -5052,7 +6518,7 @@
         <v>35</v>
       </c>
       <c r="R44" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="45" spans="13:18">
@@ -5060,10 +6526,10 @@
         <v>17</v>
       </c>
       <c r="N45" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="O45" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="P45" t="s">
         <v>25</v>
@@ -5072,7 +6538,7 @@
         <v>35</v>
       </c>
       <c r="R45" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="46" spans="13:18">
@@ -5080,10 +6546,10 @@
         <v>17</v>
       </c>
       <c r="N46" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="O46" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="P46" t="s">
         <v>25</v>
@@ -5092,7 +6558,7 @@
         <v>35</v>
       </c>
       <c r="R46" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="47" spans="13:18">
@@ -5100,10 +6566,10 @@
         <v>17</v>
       </c>
       <c r="N47" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="O47" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="P47" t="s">
         <v>25</v>
@@ -5112,7 +6578,7 @@
         <v>35</v>
       </c>
       <c r="R47" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="48" spans="13:18">
@@ -5120,10 +6586,10 @@
         <v>17</v>
       </c>
       <c r="N48" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="O48" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="P48" t="s">
         <v>25</v>
@@ -5132,7 +6598,7 @@
         <v>35</v>
       </c>
       <c r="R48" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="49" spans="13:18">
@@ -5140,10 +6606,10 @@
         <v>17</v>
       </c>
       <c r="N49" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="O49" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="P49" t="s">
         <v>25</v>
@@ -5152,7 +6618,7 @@
         <v>35</v>
       </c>
       <c r="R49" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="50" spans="13:18">
@@ -5160,10 +6626,10 @@
         <v>17</v>
       </c>
       <c r="N50" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="O50" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="P50" t="s">
         <v>25</v>
@@ -5172,7 +6638,7 @@
         <v>35</v>
       </c>
       <c r="R50" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="51" spans="13:18">
@@ -5180,10 +6646,10 @@
         <v>17</v>
       </c>
       <c r="N51" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="O51" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="P51" t="s">
         <v>25</v>
@@ -5192,7 +6658,7 @@
         <v>35</v>
       </c>
       <c r="R51" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="52" spans="13:18">
@@ -5200,10 +6666,10 @@
         <v>17</v>
       </c>
       <c r="N52" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="O52" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="P52" t="s">
         <v>25</v>
@@ -5212,7 +6678,7 @@
         <v>35</v>
       </c>
       <c r="R52" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="53" spans="13:18">
@@ -5220,10 +6686,10 @@
         <v>17</v>
       </c>
       <c r="N53" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="O53" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="P53" t="s">
         <v>25</v>
@@ -5232,7 +6698,7 @@
         <v>35</v>
       </c>
       <c r="R53" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="54" spans="13:18">
@@ -5240,10 +6706,10 @@
         <v>17</v>
       </c>
       <c r="N54" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="O54" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="P54" t="s">
         <v>25</v>
@@ -5252,7 +6718,7 @@
         <v>35</v>
       </c>
       <c r="R54" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="55" spans="13:18">
@@ -5260,10 +6726,10 @@
         <v>17</v>
       </c>
       <c r="N55" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="O55" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="P55" t="s">
         <v>25</v>
@@ -5272,7 +6738,7 @@
         <v>35</v>
       </c>
       <c r="R55" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="56" spans="13:18">
@@ -5280,10 +6746,10 @@
         <v>17</v>
       </c>
       <c r="N56" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="O56" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="P56" t="s">
         <v>25</v>
@@ -5292,7 +6758,7 @@
         <v>35</v>
       </c>
       <c r="R56" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="57" spans="13:18">
@@ -5300,10 +6766,10 @@
         <v>17</v>
       </c>
       <c r="N57" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="O57" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="P57" t="s">
         <v>25</v>
@@ -5312,7 +6778,7 @@
         <v>35</v>
       </c>
       <c r="R57" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="58" spans="13:18">
@@ -5320,10 +6786,10 @@
         <v>17</v>
       </c>
       <c r="N58" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="O58" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="P58" t="s">
         <v>25</v>
@@ -5332,7 +6798,7 @@
         <v>35</v>
       </c>
       <c r="R58" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="59" spans="13:18">
@@ -5340,10 +6806,10 @@
         <v>17</v>
       </c>
       <c r="N59" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="O59" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="P59" t="s">
         <v>25</v>
@@ -5352,7 +6818,7 @@
         <v>35</v>
       </c>
       <c r="R59" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="60" spans="13:18">
@@ -5360,10 +6826,10 @@
         <v>17</v>
       </c>
       <c r="N60" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="O60" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="P60" t="s">
         <v>25</v>
@@ -5372,7 +6838,7 @@
         <v>35</v>
       </c>
       <c r="R60" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="61" spans="13:18">
@@ -5380,10 +6846,10 @@
         <v>17</v>
       </c>
       <c r="N61" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="O61" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="P61" t="s">
         <v>25</v>
@@ -5392,7 +6858,7 @@
         <v>35</v>
       </c>
       <c r="R61" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="62" spans="13:18">
@@ -5400,10 +6866,10 @@
         <v>17</v>
       </c>
       <c r="N62" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="O62" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="P62" t="s">
         <v>25</v>
@@ -5412,7 +6878,7 @@
         <v>35</v>
       </c>
       <c r="R62" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="63" spans="13:18">
@@ -5420,10 +6886,10 @@
         <v>17</v>
       </c>
       <c r="N63" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="O63" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="P63" t="s">
         <v>25</v>
@@ -5432,7 +6898,7 @@
         <v>35</v>
       </c>
       <c r="R63" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="64" spans="13:18">
@@ -5440,10 +6906,10 @@
         <v>17</v>
       </c>
       <c r="N64" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="O64" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="P64" t="s">
         <v>25</v>
@@ -5452,7 +6918,7 @@
         <v>35</v>
       </c>
       <c r="R64" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="65" spans="13:18">
@@ -5460,10 +6926,10 @@
         <v>17</v>
       </c>
       <c r="N65" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="O65" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="P65" t="s">
         <v>25</v>
@@ -5472,7 +6938,7 @@
         <v>35</v>
       </c>
       <c r="R65" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="66" spans="13:18">
@@ -5480,10 +6946,10 @@
         <v>17</v>
       </c>
       <c r="N66" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="O66" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="P66" t="s">
         <v>25</v>
@@ -5492,7 +6958,7 @@
         <v>35</v>
       </c>
       <c r="R66" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="67" spans="13:18">
@@ -5500,10 +6966,10 @@
         <v>17</v>
       </c>
       <c r="N67" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="O67" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="P67" t="s">
         <v>25</v>
@@ -5512,7 +6978,7 @@
         <v>35</v>
       </c>
       <c r="R67" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="68" spans="13:18">
@@ -5520,10 +6986,10 @@
         <v>17</v>
       </c>
       <c r="N68" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="O68" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="P68" t="s">
         <v>25</v>
@@ -5532,7 +6998,7 @@
         <v>35</v>
       </c>
       <c r="R68" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="69" spans="13:18">
@@ -5540,10 +7006,10 @@
         <v>17</v>
       </c>
       <c r="N69" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="O69" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="P69" t="s">
         <v>25</v>
@@ -5552,7 +7018,7 @@
         <v>35</v>
       </c>
       <c r="R69" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="70" spans="13:18">
@@ -5560,10 +7026,10 @@
         <v>17</v>
       </c>
       <c r="N70" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="O70" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="P70" t="s">
         <v>25</v>
@@ -5572,7 +7038,7 @@
         <v>35</v>
       </c>
       <c r="R70" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="71" spans="13:18">
@@ -5580,10 +7046,10 @@
         <v>17</v>
       </c>
       <c r="N71" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="O71" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="P71" t="s">
         <v>25</v>
@@ -5592,7 +7058,7 @@
         <v>35</v>
       </c>
       <c r="R71" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="72" spans="13:18">
@@ -5600,10 +7066,10 @@
         <v>17</v>
       </c>
       <c r="N72" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="O72" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="P72" t="s">
         <v>25</v>
@@ -5612,7 +7078,7 @@
         <v>35</v>
       </c>
       <c r="R72" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="73" spans="13:18">
@@ -5620,10 +7086,10 @@
         <v>17</v>
       </c>
       <c r="N73" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="O73" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="P73" t="s">
         <v>25</v>
@@ -5632,7 +7098,7 @@
         <v>35</v>
       </c>
       <c r="R73" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="74" spans="13:18">
@@ -5640,10 +7106,10 @@
         <v>17</v>
       </c>
       <c r="N74" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="O74" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="P74" t="s">
         <v>25</v>
@@ -5652,7 +7118,7 @@
         <v>35</v>
       </c>
       <c r="R74" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="75" spans="13:18">
@@ -5660,10 +7126,10 @@
         <v>17</v>
       </c>
       <c r="N75" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="O75" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="P75" t="s">
         <v>25</v>
@@ -5672,7 +7138,7 @@
         <v>35</v>
       </c>
       <c r="R75" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="76" spans="13:18">
@@ -5680,10 +7146,10 @@
         <v>17</v>
       </c>
       <c r="N76" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="O76" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="P76" t="s">
         <v>25</v>
@@ -5692,7 +7158,7 @@
         <v>35</v>
       </c>
       <c r="R76" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="77" spans="13:18">
@@ -5700,10 +7166,10 @@
         <v>17</v>
       </c>
       <c r="N77" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="O77" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="P77" t="s">
         <v>25</v>
@@ -5712,7 +7178,7 @@
         <v>35</v>
       </c>
       <c r="R77" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
   </sheetData>
@@ -5723,7 +7189,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A39735C-B147-4873-BE33-BF7570891F36}">
   <dimension ref="B3:G33"/>
   <sheetFormatPr defaultColWidth="11.3984375" defaultRowHeight="12.75"/>
@@ -5998,1470 +7464,6 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E76E5488-4E38-4FD7-B484-20D8479AFFBE}">
-  <dimension ref="B3:H66"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
-  <sheetData>
-    <row r="3" spans="2:8">
-      <c r="B3" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="4" spans="2:8">
-      <c r="B4" t="s">
-        <v>214</v>
-      </c>
-      <c r="C4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="2:8">
-      <c r="B5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" t="s">
-        <v>363</v>
-      </c>
-      <c r="D5" t="s">
-        <v>364</v>
-      </c>
-      <c r="E5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F5" t="s">
-        <v>35</v>
-      </c>
-      <c r="G5" t="s">
-        <v>365</v>
-      </c>
-      <c r="H5" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="6" spans="2:8">
-      <c r="B6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" t="s">
-        <v>366</v>
-      </c>
-      <c r="D6" t="s">
-        <v>367</v>
-      </c>
-      <c r="E6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F6" t="s">
-        <v>35</v>
-      </c>
-      <c r="G6" t="s">
-        <v>365</v>
-      </c>
-      <c r="H6" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="7" spans="2:8">
-      <c r="B7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" t="s">
-        <v>368</v>
-      </c>
-      <c r="D7" t="s">
-        <v>369</v>
-      </c>
-      <c r="E7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7" t="s">
-        <v>35</v>
-      </c>
-      <c r="G7" t="s">
-        <v>365</v>
-      </c>
-      <c r="H7" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="8" spans="2:8">
-      <c r="B8" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" t="s">
-        <v>370</v>
-      </c>
-      <c r="D8" t="s">
-        <v>371</v>
-      </c>
-      <c r="E8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F8" t="s">
-        <v>35</v>
-      </c>
-      <c r="G8" t="s">
-        <v>365</v>
-      </c>
-      <c r="H8" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="9" spans="2:8">
-      <c r="B9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" t="s">
-        <v>372</v>
-      </c>
-      <c r="D9" t="s">
-        <v>373</v>
-      </c>
-      <c r="E9" t="s">
-        <v>25</v>
-      </c>
-      <c r="F9" t="s">
-        <v>35</v>
-      </c>
-      <c r="G9" t="s">
-        <v>365</v>
-      </c>
-      <c r="H9" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="10" spans="2:8">
-      <c r="B10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10" t="s">
-        <v>374</v>
-      </c>
-      <c r="D10" t="s">
-        <v>375</v>
-      </c>
-      <c r="E10" t="s">
-        <v>25</v>
-      </c>
-      <c r="F10" t="s">
-        <v>35</v>
-      </c>
-      <c r="G10" t="s">
-        <v>365</v>
-      </c>
-      <c r="H10" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="11" spans="2:8">
-      <c r="B11" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" t="s">
-        <v>376</v>
-      </c>
-      <c r="D11" t="s">
-        <v>377</v>
-      </c>
-      <c r="E11" t="s">
-        <v>25</v>
-      </c>
-      <c r="F11" t="s">
-        <v>35</v>
-      </c>
-      <c r="G11" t="s">
-        <v>365</v>
-      </c>
-      <c r="H11" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="12" spans="2:8">
-      <c r="B12" t="s">
-        <v>17</v>
-      </c>
-      <c r="C12" t="s">
-        <v>378</v>
-      </c>
-      <c r="D12" t="s">
-        <v>379</v>
-      </c>
-      <c r="E12" t="s">
-        <v>25</v>
-      </c>
-      <c r="F12" t="s">
-        <v>35</v>
-      </c>
-      <c r="G12" t="s">
-        <v>365</v>
-      </c>
-      <c r="H12" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="13" spans="2:8">
-      <c r="B13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13" t="s">
-        <v>380</v>
-      </c>
-      <c r="D13" t="s">
-        <v>381</v>
-      </c>
-      <c r="E13" t="s">
-        <v>25</v>
-      </c>
-      <c r="F13" t="s">
-        <v>35</v>
-      </c>
-      <c r="G13" t="s">
-        <v>365</v>
-      </c>
-      <c r="H13" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="14" spans="2:8">
-      <c r="B14" t="s">
-        <v>17</v>
-      </c>
-      <c r="C14" t="s">
-        <v>382</v>
-      </c>
-      <c r="D14" t="s">
-        <v>383</v>
-      </c>
-      <c r="E14" t="s">
-        <v>25</v>
-      </c>
-      <c r="F14" t="s">
-        <v>35</v>
-      </c>
-      <c r="G14" t="s">
-        <v>365</v>
-      </c>
-      <c r="H14" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="15" spans="2:8">
-      <c r="B15" t="s">
-        <v>17</v>
-      </c>
-      <c r="C15" t="s">
-        <v>384</v>
-      </c>
-      <c r="D15" t="s">
-        <v>385</v>
-      </c>
-      <c r="E15" t="s">
-        <v>25</v>
-      </c>
-      <c r="F15" t="s">
-        <v>35</v>
-      </c>
-      <c r="G15" t="s">
-        <v>365</v>
-      </c>
-      <c r="H15" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="16" spans="2:8">
-      <c r="B16" t="s">
-        <v>17</v>
-      </c>
-      <c r="C16" t="s">
-        <v>386</v>
-      </c>
-      <c r="D16" t="s">
-        <v>387</v>
-      </c>
-      <c r="E16" t="s">
-        <v>25</v>
-      </c>
-      <c r="F16" t="s">
-        <v>35</v>
-      </c>
-      <c r="G16" t="s">
-        <v>365</v>
-      </c>
-      <c r="H16" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="17" spans="2:8">
-      <c r="B17" t="s">
-        <v>17</v>
-      </c>
-      <c r="C17" t="s">
-        <v>388</v>
-      </c>
-      <c r="D17" t="s">
-        <v>389</v>
-      </c>
-      <c r="E17" t="s">
-        <v>25</v>
-      </c>
-      <c r="F17" t="s">
-        <v>35</v>
-      </c>
-      <c r="G17" t="s">
-        <v>365</v>
-      </c>
-      <c r="H17" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="18" spans="2:8">
-      <c r="B18" t="s">
-        <v>17</v>
-      </c>
-      <c r="C18" t="s">
-        <v>390</v>
-      </c>
-      <c r="D18" t="s">
-        <v>391</v>
-      </c>
-      <c r="E18" t="s">
-        <v>25</v>
-      </c>
-      <c r="F18" t="s">
-        <v>35</v>
-      </c>
-      <c r="G18" t="s">
-        <v>365</v>
-      </c>
-      <c r="H18" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="19" spans="2:8">
-      <c r="B19" t="s">
-        <v>17</v>
-      </c>
-      <c r="C19" t="s">
-        <v>392</v>
-      </c>
-      <c r="D19" t="s">
-        <v>393</v>
-      </c>
-      <c r="E19" t="s">
-        <v>25</v>
-      </c>
-      <c r="F19" t="s">
-        <v>35</v>
-      </c>
-      <c r="G19" t="s">
-        <v>365</v>
-      </c>
-      <c r="H19" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="20" spans="2:8">
-      <c r="B20" t="s">
-        <v>17</v>
-      </c>
-      <c r="C20" t="s">
-        <v>394</v>
-      </c>
-      <c r="D20" t="s">
-        <v>395</v>
-      </c>
-      <c r="E20" t="s">
-        <v>25</v>
-      </c>
-      <c r="F20" t="s">
-        <v>35</v>
-      </c>
-      <c r="G20" t="s">
-        <v>365</v>
-      </c>
-      <c r="H20" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="21" spans="2:8">
-      <c r="B21" t="s">
-        <v>17</v>
-      </c>
-      <c r="C21" t="s">
-        <v>396</v>
-      </c>
-      <c r="D21" t="s">
-        <v>397</v>
-      </c>
-      <c r="E21" t="s">
-        <v>25</v>
-      </c>
-      <c r="F21" t="s">
-        <v>35</v>
-      </c>
-      <c r="G21" t="s">
-        <v>365</v>
-      </c>
-      <c r="H21" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="22" spans="2:8">
-      <c r="B22" t="s">
-        <v>17</v>
-      </c>
-      <c r="C22" t="s">
-        <v>398</v>
-      </c>
-      <c r="D22" t="s">
-        <v>399</v>
-      </c>
-      <c r="E22" t="s">
-        <v>25</v>
-      </c>
-      <c r="F22" t="s">
-        <v>35</v>
-      </c>
-      <c r="G22" t="s">
-        <v>365</v>
-      </c>
-      <c r="H22" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="23" spans="2:8">
-      <c r="B23" t="s">
-        <v>17</v>
-      </c>
-      <c r="C23" t="s">
-        <v>400</v>
-      </c>
-      <c r="D23" t="s">
-        <v>401</v>
-      </c>
-      <c r="E23" t="s">
-        <v>25</v>
-      </c>
-      <c r="F23" t="s">
-        <v>35</v>
-      </c>
-      <c r="G23" t="s">
-        <v>365</v>
-      </c>
-      <c r="H23" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="24" spans="2:8">
-      <c r="B24" t="s">
-        <v>17</v>
-      </c>
-      <c r="C24" t="s">
-        <v>402</v>
-      </c>
-      <c r="D24" t="s">
-        <v>403</v>
-      </c>
-      <c r="E24" t="s">
-        <v>25</v>
-      </c>
-      <c r="F24" t="s">
-        <v>35</v>
-      </c>
-      <c r="G24" t="s">
-        <v>365</v>
-      </c>
-      <c r="H24" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="25" spans="2:8">
-      <c r="B25" t="s">
-        <v>17</v>
-      </c>
-      <c r="C25" t="s">
-        <v>404</v>
-      </c>
-      <c r="D25" t="s">
-        <v>405</v>
-      </c>
-      <c r="E25" t="s">
-        <v>25</v>
-      </c>
-      <c r="F25" t="s">
-        <v>35</v>
-      </c>
-      <c r="G25" t="s">
-        <v>365</v>
-      </c>
-      <c r="H25" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="26" spans="2:8">
-      <c r="B26" t="s">
-        <v>17</v>
-      </c>
-      <c r="C26" t="s">
-        <v>406</v>
-      </c>
-      <c r="D26" t="s">
-        <v>407</v>
-      </c>
-      <c r="E26" t="s">
-        <v>25</v>
-      </c>
-      <c r="F26" t="s">
-        <v>35</v>
-      </c>
-      <c r="G26" t="s">
-        <v>365</v>
-      </c>
-      <c r="H26" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="27" spans="2:8">
-      <c r="B27" t="s">
-        <v>17</v>
-      </c>
-      <c r="C27" t="s">
-        <v>408</v>
-      </c>
-      <c r="D27" t="s">
-        <v>409</v>
-      </c>
-      <c r="E27" t="s">
-        <v>25</v>
-      </c>
-      <c r="F27" t="s">
-        <v>35</v>
-      </c>
-      <c r="G27" t="s">
-        <v>365</v>
-      </c>
-      <c r="H27" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="28" spans="2:8">
-      <c r="B28" t="s">
-        <v>17</v>
-      </c>
-      <c r="C28" t="s">
-        <v>410</v>
-      </c>
-      <c r="D28" t="s">
-        <v>411</v>
-      </c>
-      <c r="E28" t="s">
-        <v>25</v>
-      </c>
-      <c r="F28" t="s">
-        <v>35</v>
-      </c>
-      <c r="G28" t="s">
-        <v>365</v>
-      </c>
-      <c r="H28" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="29" spans="2:8">
-      <c r="B29" t="s">
-        <v>17</v>
-      </c>
-      <c r="C29" t="s">
-        <v>412</v>
-      </c>
-      <c r="D29" t="s">
-        <v>413</v>
-      </c>
-      <c r="E29" t="s">
-        <v>25</v>
-      </c>
-      <c r="F29" t="s">
-        <v>35</v>
-      </c>
-      <c r="G29" t="s">
-        <v>365</v>
-      </c>
-      <c r="H29" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="30" spans="2:8">
-      <c r="B30" t="s">
-        <v>17</v>
-      </c>
-      <c r="C30" t="s">
-        <v>414</v>
-      </c>
-      <c r="D30" t="s">
-        <v>415</v>
-      </c>
-      <c r="E30" t="s">
-        <v>25</v>
-      </c>
-      <c r="F30" t="s">
-        <v>35</v>
-      </c>
-      <c r="G30" t="s">
-        <v>365</v>
-      </c>
-      <c r="H30" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="31" spans="2:8">
-      <c r="B31" t="s">
-        <v>17</v>
-      </c>
-      <c r="C31" t="s">
-        <v>416</v>
-      </c>
-      <c r="D31" t="s">
-        <v>417</v>
-      </c>
-      <c r="E31" t="s">
-        <v>25</v>
-      </c>
-      <c r="F31" t="s">
-        <v>35</v>
-      </c>
-      <c r="G31" t="s">
-        <v>365</v>
-      </c>
-      <c r="H31" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="32" spans="2:8">
-      <c r="B32" t="s">
-        <v>17</v>
-      </c>
-      <c r="C32" t="s">
-        <v>418</v>
-      </c>
-      <c r="D32" t="s">
-        <v>419</v>
-      </c>
-      <c r="E32" t="s">
-        <v>25</v>
-      </c>
-      <c r="F32" t="s">
-        <v>35</v>
-      </c>
-      <c r="G32" t="s">
-        <v>365</v>
-      </c>
-      <c r="H32" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="33" spans="2:8">
-      <c r="B33" t="s">
-        <v>17</v>
-      </c>
-      <c r="C33" t="s">
-        <v>420</v>
-      </c>
-      <c r="D33" t="s">
-        <v>421</v>
-      </c>
-      <c r="E33" t="s">
-        <v>25</v>
-      </c>
-      <c r="F33" t="s">
-        <v>35</v>
-      </c>
-      <c r="G33" t="s">
-        <v>365</v>
-      </c>
-      <c r="H33" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="34" spans="2:8">
-      <c r="B34" t="s">
-        <v>17</v>
-      </c>
-      <c r="C34" t="s">
-        <v>422</v>
-      </c>
-      <c r="D34" t="s">
-        <v>423</v>
-      </c>
-      <c r="E34" t="s">
-        <v>25</v>
-      </c>
-      <c r="F34" t="s">
-        <v>35</v>
-      </c>
-      <c r="G34" t="s">
-        <v>365</v>
-      </c>
-      <c r="H34" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="35" spans="2:8">
-      <c r="B35" t="s">
-        <v>17</v>
-      </c>
-      <c r="C35" t="s">
-        <v>424</v>
-      </c>
-      <c r="D35" t="s">
-        <v>425</v>
-      </c>
-      <c r="E35" t="s">
-        <v>25</v>
-      </c>
-      <c r="F35" t="s">
-        <v>35</v>
-      </c>
-      <c r="G35" t="s">
-        <v>365</v>
-      </c>
-      <c r="H35" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="36" spans="2:8">
-      <c r="B36" t="s">
-        <v>17</v>
-      </c>
-      <c r="C36" t="s">
-        <v>426</v>
-      </c>
-      <c r="D36" t="s">
-        <v>427</v>
-      </c>
-      <c r="E36" t="s">
-        <v>25</v>
-      </c>
-      <c r="F36" t="s">
-        <v>35</v>
-      </c>
-      <c r="G36" t="s">
-        <v>365</v>
-      </c>
-      <c r="H36" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="37" spans="2:8">
-      <c r="B37" t="s">
-        <v>17</v>
-      </c>
-      <c r="C37" t="s">
-        <v>428</v>
-      </c>
-      <c r="D37" t="s">
-        <v>429</v>
-      </c>
-      <c r="E37" t="s">
-        <v>25</v>
-      </c>
-      <c r="F37" t="s">
-        <v>35</v>
-      </c>
-      <c r="G37" t="s">
-        <v>365</v>
-      </c>
-      <c r="H37" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="38" spans="2:8">
-      <c r="B38" t="s">
-        <v>17</v>
-      </c>
-      <c r="C38" t="s">
-        <v>430</v>
-      </c>
-      <c r="D38" t="s">
-        <v>431</v>
-      </c>
-      <c r="E38" t="s">
-        <v>25</v>
-      </c>
-      <c r="F38" t="s">
-        <v>35</v>
-      </c>
-      <c r="G38" t="s">
-        <v>365</v>
-      </c>
-      <c r="H38" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="39" spans="2:8">
-      <c r="B39" t="s">
-        <v>17</v>
-      </c>
-      <c r="C39" t="s">
-        <v>432</v>
-      </c>
-      <c r="D39" t="s">
-        <v>433</v>
-      </c>
-      <c r="E39" t="s">
-        <v>25</v>
-      </c>
-      <c r="F39" t="s">
-        <v>35</v>
-      </c>
-      <c r="G39" t="s">
-        <v>365</v>
-      </c>
-      <c r="H39" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="40" spans="2:8">
-      <c r="B40" t="s">
-        <v>17</v>
-      </c>
-      <c r="C40" t="s">
-        <v>434</v>
-      </c>
-      <c r="D40" t="s">
-        <v>435</v>
-      </c>
-      <c r="E40" t="s">
-        <v>25</v>
-      </c>
-      <c r="F40" t="s">
-        <v>35</v>
-      </c>
-      <c r="G40" t="s">
-        <v>365</v>
-      </c>
-      <c r="H40" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="41" spans="2:8">
-      <c r="B41" t="s">
-        <v>17</v>
-      </c>
-      <c r="C41" t="s">
-        <v>436</v>
-      </c>
-      <c r="D41" t="s">
-        <v>437</v>
-      </c>
-      <c r="E41" t="s">
-        <v>25</v>
-      </c>
-      <c r="F41" t="s">
-        <v>35</v>
-      </c>
-      <c r="G41" t="s">
-        <v>365</v>
-      </c>
-      <c r="H41" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="42" spans="2:8">
-      <c r="B42" t="s">
-        <v>17</v>
-      </c>
-      <c r="C42" t="s">
-        <v>438</v>
-      </c>
-      <c r="D42" t="s">
-        <v>439</v>
-      </c>
-      <c r="E42" t="s">
-        <v>25</v>
-      </c>
-      <c r="F42" t="s">
-        <v>35</v>
-      </c>
-      <c r="G42" t="s">
-        <v>365</v>
-      </c>
-      <c r="H42" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="43" spans="2:8">
-      <c r="B43" t="s">
-        <v>17</v>
-      </c>
-      <c r="C43" t="s">
-        <v>440</v>
-      </c>
-      <c r="D43" t="s">
-        <v>441</v>
-      </c>
-      <c r="E43" t="s">
-        <v>25</v>
-      </c>
-      <c r="F43" t="s">
-        <v>35</v>
-      </c>
-      <c r="G43" t="s">
-        <v>365</v>
-      </c>
-      <c r="H43" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="44" spans="2:8">
-      <c r="B44" t="s">
-        <v>17</v>
-      </c>
-      <c r="C44" t="s">
-        <v>442</v>
-      </c>
-      <c r="D44" t="s">
-        <v>443</v>
-      </c>
-      <c r="E44" t="s">
-        <v>25</v>
-      </c>
-      <c r="F44" t="s">
-        <v>35</v>
-      </c>
-      <c r="G44" t="s">
-        <v>365</v>
-      </c>
-      <c r="H44" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="45" spans="2:8">
-      <c r="B45" t="s">
-        <v>17</v>
-      </c>
-      <c r="C45" t="s">
-        <v>444</v>
-      </c>
-      <c r="D45" t="s">
-        <v>445</v>
-      </c>
-      <c r="E45" t="s">
-        <v>25</v>
-      </c>
-      <c r="F45" t="s">
-        <v>35</v>
-      </c>
-      <c r="G45" t="s">
-        <v>365</v>
-      </c>
-      <c r="H45" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="46" spans="2:8">
-      <c r="B46" t="s">
-        <v>17</v>
-      </c>
-      <c r="C46" t="s">
-        <v>446</v>
-      </c>
-      <c r="D46" t="s">
-        <v>447</v>
-      </c>
-      <c r="E46" t="s">
-        <v>25</v>
-      </c>
-      <c r="F46" t="s">
-        <v>35</v>
-      </c>
-      <c r="G46" t="s">
-        <v>365</v>
-      </c>
-      <c r="H46" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="47" spans="2:8">
-      <c r="B47" t="s">
-        <v>17</v>
-      </c>
-      <c r="C47" t="s">
-        <v>448</v>
-      </c>
-      <c r="D47" t="s">
-        <v>449</v>
-      </c>
-      <c r="E47" t="s">
-        <v>25</v>
-      </c>
-      <c r="F47" t="s">
-        <v>35</v>
-      </c>
-      <c r="G47" t="s">
-        <v>365</v>
-      </c>
-      <c r="H47" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="48" spans="2:8">
-      <c r="B48" t="s">
-        <v>17</v>
-      </c>
-      <c r="C48" t="s">
-        <v>450</v>
-      </c>
-      <c r="D48" t="s">
-        <v>451</v>
-      </c>
-      <c r="E48" t="s">
-        <v>25</v>
-      </c>
-      <c r="F48" t="s">
-        <v>35</v>
-      </c>
-      <c r="G48" t="s">
-        <v>365</v>
-      </c>
-      <c r="H48" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="49" spans="2:8">
-      <c r="B49" t="s">
-        <v>17</v>
-      </c>
-      <c r="C49" t="s">
-        <v>452</v>
-      </c>
-      <c r="D49" t="s">
-        <v>453</v>
-      </c>
-      <c r="E49" t="s">
-        <v>25</v>
-      </c>
-      <c r="F49" t="s">
-        <v>35</v>
-      </c>
-      <c r="G49" t="s">
-        <v>365</v>
-      </c>
-      <c r="H49" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="50" spans="2:8">
-      <c r="B50" t="s">
-        <v>17</v>
-      </c>
-      <c r="C50" t="s">
-        <v>454</v>
-      </c>
-      <c r="D50" t="s">
-        <v>455</v>
-      </c>
-      <c r="E50" t="s">
-        <v>25</v>
-      </c>
-      <c r="F50" t="s">
-        <v>35</v>
-      </c>
-      <c r="G50" t="s">
-        <v>365</v>
-      </c>
-      <c r="H50" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="51" spans="2:8">
-      <c r="B51" t="s">
-        <v>17</v>
-      </c>
-      <c r="C51" t="s">
-        <v>456</v>
-      </c>
-      <c r="D51" t="s">
-        <v>457</v>
-      </c>
-      <c r="E51" t="s">
-        <v>25</v>
-      </c>
-      <c r="F51" t="s">
-        <v>35</v>
-      </c>
-      <c r="G51" t="s">
-        <v>365</v>
-      </c>
-      <c r="H51" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="52" spans="2:8">
-      <c r="B52" t="s">
-        <v>17</v>
-      </c>
-      <c r="C52" t="s">
-        <v>458</v>
-      </c>
-      <c r="D52" t="s">
-        <v>459</v>
-      </c>
-      <c r="E52" t="s">
-        <v>25</v>
-      </c>
-      <c r="F52" t="s">
-        <v>35</v>
-      </c>
-      <c r="G52" t="s">
-        <v>365</v>
-      </c>
-      <c r="H52" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="53" spans="2:8">
-      <c r="B53" t="s">
-        <v>17</v>
-      </c>
-      <c r="C53" t="s">
-        <v>460</v>
-      </c>
-      <c r="D53" t="s">
-        <v>461</v>
-      </c>
-      <c r="E53" t="s">
-        <v>25</v>
-      </c>
-      <c r="F53" t="s">
-        <v>35</v>
-      </c>
-      <c r="G53" t="s">
-        <v>365</v>
-      </c>
-      <c r="H53" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="54" spans="2:8">
-      <c r="B54" t="s">
-        <v>17</v>
-      </c>
-      <c r="C54" t="s">
-        <v>462</v>
-      </c>
-      <c r="D54" t="s">
-        <v>463</v>
-      </c>
-      <c r="E54" t="s">
-        <v>25</v>
-      </c>
-      <c r="F54" t="s">
-        <v>35</v>
-      </c>
-      <c r="G54" t="s">
-        <v>365</v>
-      </c>
-      <c r="H54" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="55" spans="2:8">
-      <c r="B55" t="s">
-        <v>17</v>
-      </c>
-      <c r="C55" t="s">
-        <v>464</v>
-      </c>
-      <c r="D55" t="s">
-        <v>465</v>
-      </c>
-      <c r="E55" t="s">
-        <v>25</v>
-      </c>
-      <c r="F55" t="s">
-        <v>35</v>
-      </c>
-      <c r="G55" t="s">
-        <v>365</v>
-      </c>
-      <c r="H55" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="56" spans="2:8">
-      <c r="B56" t="s">
-        <v>17</v>
-      </c>
-      <c r="C56" t="s">
-        <v>466</v>
-      </c>
-      <c r="D56" t="s">
-        <v>467</v>
-      </c>
-      <c r="E56" t="s">
-        <v>25</v>
-      </c>
-      <c r="F56" t="s">
-        <v>35</v>
-      </c>
-      <c r="G56" t="s">
-        <v>365</v>
-      </c>
-      <c r="H56" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="57" spans="2:8">
-      <c r="B57" t="s">
-        <v>17</v>
-      </c>
-      <c r="C57" t="s">
-        <v>468</v>
-      </c>
-      <c r="D57" t="s">
-        <v>469</v>
-      </c>
-      <c r="E57" t="s">
-        <v>25</v>
-      </c>
-      <c r="F57" t="s">
-        <v>35</v>
-      </c>
-      <c r="G57" t="s">
-        <v>365</v>
-      </c>
-      <c r="H57" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="58" spans="2:8">
-      <c r="B58" t="s">
-        <v>17</v>
-      </c>
-      <c r="C58" t="s">
-        <v>470</v>
-      </c>
-      <c r="D58" t="s">
-        <v>471</v>
-      </c>
-      <c r="E58" t="s">
-        <v>25</v>
-      </c>
-      <c r="F58" t="s">
-        <v>35</v>
-      </c>
-      <c r="G58" t="s">
-        <v>365</v>
-      </c>
-      <c r="H58" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="59" spans="2:8">
-      <c r="B59" t="s">
-        <v>17</v>
-      </c>
-      <c r="C59" t="s">
-        <v>472</v>
-      </c>
-      <c r="D59" t="s">
-        <v>473</v>
-      </c>
-      <c r="E59" t="s">
-        <v>25</v>
-      </c>
-      <c r="F59" t="s">
-        <v>35</v>
-      </c>
-      <c r="G59" t="s">
-        <v>365</v>
-      </c>
-      <c r="H59" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="60" spans="2:8">
-      <c r="B60" t="s">
-        <v>17</v>
-      </c>
-      <c r="C60" t="s">
-        <v>474</v>
-      </c>
-      <c r="D60" t="s">
-        <v>475</v>
-      </c>
-      <c r="E60" t="s">
-        <v>25</v>
-      </c>
-      <c r="F60" t="s">
-        <v>35</v>
-      </c>
-      <c r="G60" t="s">
-        <v>365</v>
-      </c>
-      <c r="H60" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="61" spans="2:8">
-      <c r="B61" t="s">
-        <v>17</v>
-      </c>
-      <c r="C61" t="s">
-        <v>476</v>
-      </c>
-      <c r="D61" t="s">
-        <v>477</v>
-      </c>
-      <c r="E61" t="s">
-        <v>25</v>
-      </c>
-      <c r="F61" t="s">
-        <v>35</v>
-      </c>
-      <c r="G61" t="s">
-        <v>365</v>
-      </c>
-      <c r="H61" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="62" spans="2:8">
-      <c r="B62" t="s">
-        <v>17</v>
-      </c>
-      <c r="C62" t="s">
-        <v>478</v>
-      </c>
-      <c r="D62" t="s">
-        <v>479</v>
-      </c>
-      <c r="E62" t="s">
-        <v>25</v>
-      </c>
-      <c r="F62" t="s">
-        <v>35</v>
-      </c>
-      <c r="G62" t="s">
-        <v>365</v>
-      </c>
-      <c r="H62" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="63" spans="2:8">
-      <c r="B63" t="s">
-        <v>17</v>
-      </c>
-      <c r="C63" t="s">
-        <v>480</v>
-      </c>
-      <c r="D63" t="s">
-        <v>481</v>
-      </c>
-      <c r="E63" t="s">
-        <v>25</v>
-      </c>
-      <c r="F63" t="s">
-        <v>35</v>
-      </c>
-      <c r="G63" t="s">
-        <v>365</v>
-      </c>
-      <c r="H63" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="64" spans="2:8">
-      <c r="B64" t="s">
-        <v>17</v>
-      </c>
-      <c r="C64" t="s">
-        <v>482</v>
-      </c>
-      <c r="D64" t="s">
-        <v>483</v>
-      </c>
-      <c r="E64" t="s">
-        <v>25</v>
-      </c>
-      <c r="F64" t="s">
-        <v>35</v>
-      </c>
-      <c r="G64" t="s">
-        <v>365</v>
-      </c>
-      <c r="H64" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="65" spans="2:8">
-      <c r="B65" t="s">
-        <v>17</v>
-      </c>
-      <c r="C65" t="s">
-        <v>484</v>
-      </c>
-      <c r="D65" t="s">
-        <v>485</v>
-      </c>
-      <c r="E65" t="s">
-        <v>25</v>
-      </c>
-      <c r="F65" t="s">
-        <v>35</v>
-      </c>
-      <c r="G65" t="s">
-        <v>365</v>
-      </c>
-      <c r="H65" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="66" spans="2:8">
-      <c r="B66" t="s">
-        <v>17</v>
-      </c>
-      <c r="C66" t="s">
-        <v>486</v>
-      </c>
-      <c r="D66" t="s">
-        <v>487</v>
-      </c>
-      <c r="E66" t="s">
-        <v>25</v>
-      </c>
-      <c r="F66" t="s">
-        <v>35</v>
-      </c>
-      <c r="G66" t="s">
-        <v>365</v>
-      </c>
-      <c r="H66" t="s">
-        <v>217</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 

--- a/VerveStacks_NGA_grids_kan/SysSettings.xlsx
+++ b/VerveStacks_NGA_grids_kan/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NGA_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2775E1F-AF69-4C07-8127-8EDB4CE9DC29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBE3B310-5A29-4F4B-93A1-06FFBFFCF084}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3935,7 +3935,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E833400-FB26-49F4-9409-80FCE2D46259}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{745330EA-72BE-4A35-BDFF-8F0517976438}">
   <dimension ref="B3:H66"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
